--- a/moduli_aziende/aifecs/moduli_compilati/REG-DOC-Registro_Documenti_SGQ.xlsx
+++ b/moduli_aziende/aifecs/moduli_compilati/REG-DOC-Registro_Documenti_SGQ.xlsx
@@ -2,26 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0cc14da05b3c4e0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rab88c7da5765422c"/>
   </x:sheets>
 </x:workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:authors>
-    <x:author/>
-  </x:authors>
-  <x:commentList>
-    <x:comment ref="A1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>AIFECS — BOZZA DA CONFERMARE. Proposta operativa per il sistema qualità ISO 9001. Ruoli, priorità, criteri e obiettivi sono proposte. I registri vanno compilati con dati ed evidenze reali. Vedere la guida e la proposta operativa del pacchetto.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-  </x:commentList>
-</x:comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -368,7 +351,7 @@
         <x:v>Note</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="68" customHeight="1">
+    <x:row r="2" ht="50" customHeight="1">
       <x:c r="A2" s="6" t="str">
         <x:v>Modulo</x:v>
       </x:c>
@@ -379,7 +362,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
         <x:v>formazione2026.xlsx</x:v>
@@ -390,16 +373,12 @@
       <x:c r="G2" s="6" t="str">
         <x:v>moduli_compilati/formazione2026.xlsx</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H2" s="6"/>
       <x:c r="I2" s="7"/>
       <x:c r="J2" s="6"/>
-      <x:c r="K2" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K2" s="6"/>
       <x:c r="L2" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="68" customHeight="1">
@@ -413,7 +392,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D3" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
         <x:v>Matrice competenze_2026.xlsx</x:v>
@@ -424,16 +403,12 @@
       <x:c r="G3" s="6" t="str">
         <x:v>moduli_compilati/Matrice competenze_2026.xlsx</x:v>
       </x:c>
-      <x:c r="H3" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H3" s="6"/>
       <x:c r="I3" s="7"/>
       <x:c r="J3" s="6"/>
-      <x:c r="K3" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K3" s="6"/>
       <x:c r="L3" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="68" customHeight="1">
@@ -447,7 +422,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D4" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
         <x:v>MOD-1020-A-Apertura_NC.xlsx</x:v>
@@ -458,16 +433,12 @@
       <x:c r="G4" s="6" t="str">
         <x:v>moduli_compilati/MOD-1020-A-Apertura_NC.xlsx</x:v>
       </x:c>
-      <x:c r="H4" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H4" s="6"/>
       <x:c r="I4" s="7"/>
       <x:c r="J4" s="6"/>
-      <x:c r="K4" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K4" s="6"/>
       <x:c r="L4" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="68" customHeight="1">
@@ -481,7 +452,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D5" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
         <x:v>MOD-1020-B-Azioni_Correttive.xlsx</x:v>
@@ -492,19 +463,15 @@
       <x:c r="G5" s="6" t="str">
         <x:v>moduli_compilati/MOD-1020-B-Azioni_Correttive.xlsx</x:v>
       </x:c>
-      <x:c r="H5" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H5" s="6"/>
       <x:c r="I5" s="7"/>
       <x:c r="J5" s="6"/>
-      <x:c r="K5" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K5" s="6"/>
       <x:c r="L5" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="68" customHeight="1">
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="50" customHeight="1">
       <x:c r="A6" s="6" t="str">
         <x:v>Modulo</x:v>
       </x:c>
@@ -515,7 +482,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D6" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
         <x:v>MOD-400-A-Contesto.xlsx</x:v>
@@ -526,16 +493,12 @@
       <x:c r="G6" s="6" t="str">
         <x:v>moduli_compilati/MOD-400-A-Contesto.xlsx</x:v>
       </x:c>
-      <x:c r="H6" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H6" s="6"/>
       <x:c r="I6" s="7"/>
       <x:c r="J6" s="6"/>
-      <x:c r="K6" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K6" s="6"/>
       <x:c r="L6" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="68" customHeight="1">
@@ -549,7 +512,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D7" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E7" s="6" t="str">
         <x:v>MOD-400-B-Parti_Interessate.xlsx</x:v>
@@ -560,16 +523,12 @@
       <x:c r="G7" s="6" t="str">
         <x:v>moduli_compilati/MOD-400-B-Parti_Interessate.xlsx</x:v>
       </x:c>
-      <x:c r="H7" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H7" s="6"/>
       <x:c r="I7" s="7"/>
       <x:c r="J7" s="6"/>
-      <x:c r="K7" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K7" s="6"/>
       <x:c r="L7" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
@@ -583,7 +542,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D8" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E8" s="6" t="str">
         <x:v>MOD-530-B-Ruoli_e_Requisiti.xlsx</x:v>
@@ -594,16 +553,12 @@
       <x:c r="G8" s="6" t="str">
         <x:v>moduli_compilati/MOD-530-B-Ruoli_e_Requisiti.xlsx</x:v>
       </x:c>
-      <x:c r="H8" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H8" s="6"/>
       <x:c r="I8" s="7"/>
       <x:c r="J8" s="6"/>
-      <x:c r="K8" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K8" s="6"/>
       <x:c r="L8" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
@@ -617,7 +572,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D9" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E9" s="6" t="str">
         <x:v>MOD-530-C-Matrice_Responsabilita.xlsx</x:v>
@@ -628,16 +583,12 @@
       <x:c r="G9" s="6" t="str">
         <x:v>moduli_compilati/MOD-530-C-Matrice_Responsabilita.xlsx</x:v>
       </x:c>
-      <x:c r="H9" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H9" s="6"/>
       <x:c r="I9" s="7"/>
       <x:c r="J9" s="6"/>
-      <x:c r="K9" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K9" s="6"/>
       <x:c r="L9" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
@@ -651,7 +602,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D10" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E10" s="6" t="str">
         <x:v>MOD-610-B-Risk_Management.xlsx</x:v>
@@ -662,16 +613,12 @@
       <x:c r="G10" s="6" t="str">
         <x:v>moduli_compilati/MOD-610-B-Risk_Management.xlsx</x:v>
       </x:c>
-      <x:c r="H10" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H10" s="6"/>
       <x:c r="I10" s="7"/>
       <x:c r="J10" s="6"/>
-      <x:c r="K10" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K10" s="6"/>
       <x:c r="L10" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
@@ -685,7 +632,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D11" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E11" s="6" t="str">
         <x:v>MOD-620-B-Pianificazione.xlsx</x:v>
@@ -696,16 +643,12 @@
       <x:c r="G11" s="6" t="str">
         <x:v>moduli_compilati/MOD-620-B-Pianificazione.xlsx</x:v>
       </x:c>
-      <x:c r="H11" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H11" s="6"/>
       <x:c r="I11" s="7"/>
       <x:c r="J11" s="6"/>
-      <x:c r="K11" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K11" s="6"/>
       <x:c r="L11" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
@@ -719,7 +662,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D12" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E12" s="6" t="str">
         <x:v>MOD-710-A-Ambienti_Lavoro.xlsx</x:v>
@@ -730,19 +673,15 @@
       <x:c r="G12" s="6" t="str">
         <x:v>moduli_compilati/MOD-710-A-Ambienti_Lavoro.xlsx</x:v>
       </x:c>
-      <x:c r="H12" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H12" s="6"/>
       <x:c r="I12" s="7"/>
       <x:c r="J12" s="6"/>
-      <x:c r="K12" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K12" s="6"/>
       <x:c r="L12" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="68" customHeight="1">
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="50" customHeight="1">
       <x:c r="A13" s="6" t="str">
         <x:v>Modulo</x:v>
       </x:c>
@@ -753,7 +692,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D13" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E13" s="6" t="str">
         <x:v>MOD-710-B-Dispositivi.xlsx</x:v>
@@ -764,16 +703,12 @@
       <x:c r="G13" s="6" t="str">
         <x:v>moduli_compilati/MOD-710-B-Dispositivi.xlsx</x:v>
       </x:c>
-      <x:c r="H13" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H13" s="6"/>
       <x:c r="I13" s="7"/>
       <x:c r="J13" s="6"/>
-      <x:c r="K13" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K13" s="6"/>
       <x:c r="L13" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
@@ -787,7 +722,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D14" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E14" s="6" t="str">
         <x:v>MOD-710-B_Dispositivi_NOMINATIVI.xlsx</x:v>
@@ -798,16 +733,12 @@
       <x:c r="G14" s="6" t="str">
         <x:v>moduli_compilati/MOD-710-B_Dispositivi_NOMINATIVI.xlsx</x:v>
       </x:c>
-      <x:c r="H14" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H14" s="6"/>
       <x:c r="I14" s="7"/>
       <x:c r="J14" s="6"/>
-      <x:c r="K14" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K14" s="6"/>
       <x:c r="L14" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="68" customHeight="1">
@@ -821,7 +752,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D15" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E15" s="6" t="str">
         <x:v>MOD-710-C-Risorse_Misurazione.xlsx</x:v>
@@ -832,16 +763,12 @@
       <x:c r="G15" s="6" t="str">
         <x:v>moduli_compilati/MOD-710-C-Risorse_Misurazione.xlsx</x:v>
       </x:c>
-      <x:c r="H15" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H15" s="6"/>
       <x:c r="I15" s="7"/>
       <x:c r="J15" s="6"/>
-      <x:c r="K15" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K15" s="6"/>
       <x:c r="L15" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="68" customHeight="1">
@@ -855,7 +782,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D16" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E16" s="6" t="str">
         <x:v>MOD-710-D-Attrezzature.xlsx</x:v>
@@ -866,16 +793,12 @@
       <x:c r="G16" s="6" t="str">
         <x:v>moduli_compilati/MOD-710-D-Attrezzature.xlsx</x:v>
       </x:c>
-      <x:c r="H16" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H16" s="6"/>
       <x:c r="I16" s="7"/>
       <x:c r="J16" s="6"/>
-      <x:c r="K16" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K16" s="6"/>
       <x:c r="L16" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="68" customHeight="1">
@@ -889,7 +812,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D17" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E17" s="6" t="str">
         <x:v>MOD-710-E-Conoscenza_Organizzativa.xlsx</x:v>
@@ -900,19 +823,15 @@
       <x:c r="G17" s="6" t="str">
         <x:v>moduli_compilati/MOD-710-E-Conoscenza_Organizzativa.xlsx</x:v>
       </x:c>
-      <x:c r="H17" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H17" s="6"/>
       <x:c r="I17" s="7"/>
       <x:c r="J17" s="6"/>
-      <x:c r="K17" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K17" s="6"/>
       <x:c r="L17" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="68" customHeight="1">
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="50" customHeight="1">
       <x:c r="A18" s="6" t="str">
         <x:v>Modulo</x:v>
       </x:c>
@@ -923,7 +842,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D18" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E18" s="6" t="str">
         <x:v>MOD-710-Supporti.xlsx</x:v>
@@ -934,16 +853,12 @@
       <x:c r="G18" s="6" t="str">
         <x:v>moduli_compilati/MOD-710-Supporti.xlsx</x:v>
       </x:c>
-      <x:c r="H18" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H18" s="6"/>
       <x:c r="I18" s="7"/>
       <x:c r="J18" s="6"/>
-      <x:c r="K18" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K18" s="6"/>
       <x:c r="L18" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="68" customHeight="1">
@@ -957,7 +872,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D19" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E19" s="6" t="str">
         <x:v>MOD-720-C-Registro_formazione.xlsx</x:v>
@@ -968,16 +883,12 @@
       <x:c r="G19" s="6" t="str">
         <x:v>moduli_compilati/MOD-720-C-Registro_formazione.xlsx</x:v>
       </x:c>
-      <x:c r="H19" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H19" s="6"/>
       <x:c r="I19" s="7"/>
       <x:c r="J19" s="6"/>
-      <x:c r="K19" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K19" s="6"/>
       <x:c r="L19" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="68" customHeight="1">
@@ -991,7 +902,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D20" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E20" s="6" t="str">
         <x:v>MOD-720-F1-Monitoraggio_Formazione.xlsx</x:v>
@@ -1002,16 +913,12 @@
       <x:c r="G20" s="6" t="str">
         <x:v>moduli_compilati/MOD-720-F1-Monitoraggio_Formazione.xlsx</x:v>
       </x:c>
-      <x:c r="H20" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H20" s="6"/>
       <x:c r="I20" s="7"/>
       <x:c r="J20" s="6"/>
-      <x:c r="K20" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K20" s="6"/>
       <x:c r="L20" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="68" customHeight="1">
@@ -1025,7 +932,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D21" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E21" s="6" t="str">
         <x:v>MOD-720-G-Piano_Formazione_Annuale.xlsx</x:v>
@@ -1036,16 +943,12 @@
       <x:c r="G21" s="6" t="str">
         <x:v>moduli_compilati/MOD-720-G-Piano_Formazione_Annuale.xlsx</x:v>
       </x:c>
-      <x:c r="H21" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H21" s="6"/>
       <x:c r="I21" s="7"/>
       <x:c r="J21" s="6"/>
-      <x:c r="K21" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K21" s="6"/>
       <x:c r="L21" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="68" customHeight="1">
@@ -1059,7 +962,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D22" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E22" s="6" t="str">
         <x:v>MOD-720-H-Anagrafica_Personale.xlsx</x:v>
@@ -1070,16 +973,12 @@
       <x:c r="G22" s="6" t="str">
         <x:v>moduli_compilati/MOD-720-H-Anagrafica_Personale.xlsx</x:v>
       </x:c>
-      <x:c r="H22" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H22" s="6"/>
       <x:c r="I22" s="7"/>
       <x:c r="J22" s="6"/>
-      <x:c r="K22" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K22" s="6"/>
       <x:c r="L22" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="68" customHeight="1">
@@ -1093,7 +992,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D23" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E23" s="6" t="str">
         <x:v>MOD-720-I-Azioni_Formative_Personale.xlsx</x:v>
@@ -1104,16 +1003,12 @@
       <x:c r="G23" s="6" t="str">
         <x:v>moduli_compilati/MOD-720-I-Azioni_Formative_Personale.xlsx</x:v>
       </x:c>
-      <x:c r="H23" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H23" s="6"/>
       <x:c r="I23" s="7"/>
       <x:c r="J23" s="6"/>
-      <x:c r="K23" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K23" s="6"/>
       <x:c r="L23" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="68" customHeight="1">
@@ -1127,7 +1022,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D24" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E24" s="6" t="str">
         <x:v>MOD-740-B-Monitoraggio_Comunicazione.xlsx</x:v>
@@ -1138,16 +1033,12 @@
       <x:c r="G24" s="6" t="str">
         <x:v>moduli_compilati/MOD-740-B-Monitoraggio_Comunicazione.xlsx</x:v>
       </x:c>
-      <x:c r="H24" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H24" s="6"/>
       <x:c r="I24" s="7"/>
       <x:c r="J24" s="6"/>
-      <x:c r="K24" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K24" s="6"/>
       <x:c r="L24" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="68" customHeight="1">
@@ -1161,7 +1052,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D25" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E25" s="6" t="str">
         <x:v>MOD-840-A-Mappatura_Fornitori.xlsx</x:v>
@@ -1172,16 +1063,12 @@
       <x:c r="G25" s="6" t="str">
         <x:v>moduli_compilati/MOD-840-A-Mappatura_Fornitori.xlsx</x:v>
       </x:c>
-      <x:c r="H25" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H25" s="6"/>
       <x:c r="I25" s="7"/>
       <x:c r="J25" s="6"/>
-      <x:c r="K25" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K25" s="6"/>
       <x:c r="L25" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="68" customHeight="1">
@@ -1195,7 +1082,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D26" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E26" s="6" t="str">
         <x:v>MOD-870-B- Registro NC.xlsx</x:v>
@@ -1206,16 +1093,12 @@
       <x:c r="G26" s="6" t="str">
         <x:v>moduli_compilati/MOD-870-B- Registro NC.xlsx</x:v>
       </x:c>
-      <x:c r="H26" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H26" s="6"/>
       <x:c r="I26" s="7"/>
       <x:c r="J26" s="6"/>
-      <x:c r="K26" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K26" s="6"/>
       <x:c r="L26" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="68" customHeight="1">
@@ -1229,7 +1112,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D27" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E27" s="6" t="str">
         <x:v>MOD-870-B-Prodotti_Non_Conformi.xlsx</x:v>
@@ -1240,19 +1123,15 @@
       <x:c r="G27" s="6" t="str">
         <x:v>moduli_compilati/MOD-870-B-Prodotti_Non_Conformi.xlsx</x:v>
       </x:c>
-      <x:c r="H27" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H27" s="6"/>
       <x:c r="I27" s="7"/>
       <x:c r="J27" s="6"/>
-      <x:c r="K27" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K27" s="6"/>
       <x:c r="L27" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="68" customHeight="1">
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="50" customHeight="1">
       <x:c r="A28" s="6" t="str">
         <x:v>Modulo</x:v>
       </x:c>
@@ -1263,7 +1142,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D28" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E28" s="6" t="str">
         <x:v>MOD-870-B-Registro_NC.xlsx</x:v>
@@ -1274,16 +1153,12 @@
       <x:c r="G28" s="6" t="str">
         <x:v>moduli_compilati/MOD-870-B-Registro_NC.xlsx</x:v>
       </x:c>
-      <x:c r="H28" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H28" s="6"/>
       <x:c r="I28" s="7"/>
       <x:c r="J28" s="6"/>
-      <x:c r="K28" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K28" s="6"/>
       <x:c r="L28" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="68" customHeight="1">
@@ -1297,7 +1172,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D29" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E29" s="6" t="str">
         <x:v>MOD-910-C-Soddisfazione_Clienti.xlsx</x:v>
@@ -1308,19 +1183,15 @@
       <x:c r="G29" s="6" t="str">
         <x:v>moduli_compilati/MOD-910-C-Soddisfazione_Clienti.xlsx</x:v>
       </x:c>
-      <x:c r="H29" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H29" s="6"/>
       <x:c r="I29" s="7"/>
       <x:c r="J29" s="6"/>
-      <x:c r="K29" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K29" s="6"/>
       <x:c r="L29" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="68" customHeight="1">
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="50" customHeight="1">
       <x:c r="A30" s="6" t="str">
         <x:v>Modulo</x:v>
       </x:c>
@@ -1331,7 +1202,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D30" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E30" s="6" t="str">
         <x:v>MOD-910-H-Performance.xlsx</x:v>
@@ -1342,16 +1213,12 @@
       <x:c r="G30" s="6" t="str">
         <x:v>moduli_compilati/MOD-910-H-Performance.xlsx</x:v>
       </x:c>
-      <x:c r="H30" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H30" s="6"/>
       <x:c r="I30" s="7"/>
       <x:c r="J30" s="6"/>
-      <x:c r="K30" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K30" s="6"/>
       <x:c r="L30" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="68" customHeight="1">
@@ -1365,7 +1232,7 @@
         <x:v>ISO 9001</x:v>
       </x:c>
       <x:c r="D31" s="6" t="str">
-        <x:v>Bozza AIFECS</x:v>
+        <x:v>Sistema qualità AIFECS</x:v>
       </x:c>
       <x:c r="E31" s="6" t="str">
         <x:v>REG-DOC-Registro_Documenti_SGQ.xlsx</x:v>
@@ -1376,41 +1243,73 @@
       <x:c r="G31" s="6" t="str">
         <x:v>moduli_compilati/REG-DOC-Registro_Documenti_SGQ.xlsx</x:v>
       </x:c>
-      <x:c r="H31" s="6" t="str">
-        <x:v>BOZZA</x:v>
-      </x:c>
+      <x:c r="H31" s="6"/>
       <x:c r="I31" s="7"/>
       <x:c r="J31" s="6"/>
-      <x:c r="K31" s="6" t="str">
-        <x:v>Da confermare</x:v>
-      </x:c>
+      <x:c r="K31" s="6"/>
       <x:c r="L31" s="6" t="str">
-        <x:v>Percorso proposto da verificare nel viewer; nessuna approvazione o revisione ufficiale attribuita.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32"/>
-      <x:c r="B32"/>
-      <x:c r="D32"/>
-      <x:c r="E32"/>
-      <x:c r="F32"/>
-      <x:c r="G32"/>
-      <x:c r="H32"/>
-      <x:c r="I32" s="2"/>
-      <x:c r="J32"/>
-      <x:c r="K32"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33"/>
-      <x:c r="B33"/>
-      <x:c r="D33"/>
-      <x:c r="E33"/>
-      <x:c r="F33"/>
-      <x:c r="G33"/>
-      <x:c r="H33"/>
-      <x:c r="I33" s="2"/>
-      <x:c r="J33"/>
-      <x:c r="K33"/>
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="50" customHeight="1">
+      <x:c r="A32" s="6" t="str">
+        <x:v>Modulo</x:v>
+      </x:c>
+      <x:c r="B32" s="6" t="str">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="C32" s="6" t="str">
+        <x:v>ISO 9001</x:v>
+      </x:c>
+      <x:c r="D32" s="6" t="str">
+        <x:v>Rischi e opportunità</x:v>
+      </x:c>
+      <x:c r="E32" s="6" t="str">
+        <x:v>Mod.01.PO.06.1_VR.xlsx</x:v>
+      </x:c>
+      <x:c r="F32" s="6" t="str">
+        <x:v>moduli_compilati/Mod.01.PO.06.1_VR.xlsx</x:v>
+      </x:c>
+      <x:c r="G32" s="6" t="str">
+        <x:v>moduli_compilati/Mod.01.PO.06.1_VR.xlsx</x:v>
+      </x:c>
+      <x:c r="H32" s="6"/>
+      <x:c r="I32" s="7"/>
+      <x:c r="J32" s="6"/>
+      <x:c r="K32" s="6"/>
+      <x:c r="L32" s="6" t="str">
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="68" customHeight="1">
+      <x:c r="A33" s="6" t="str">
+        <x:v>Modulo</x:v>
+      </x:c>
+      <x:c r="B33" s="6" t="str">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="C33" s="6" t="str">
+        <x:v>ISO 9001</x:v>
+      </x:c>
+      <x:c r="D33" s="6" t="str">
+        <x:v>Rischi e opportunità</x:v>
+      </x:c>
+      <x:c r="E33" s="6" t="str">
+        <x:v>Mod.02.PO.06.1_Risk_management.xlsx</x:v>
+      </x:c>
+      <x:c r="F33" s="6" t="str">
+        <x:v>moduli_compilati/Mod.02.PO.06.1_Risk_management.xlsx</x:v>
+      </x:c>
+      <x:c r="G33" s="6" t="str">
+        <x:v>moduli_compilati/Mod.02.PO.06.1_Risk_management.xlsx</x:v>
+      </x:c>
+      <x:c r="H33" s="6"/>
+      <x:c r="I33" s="7"/>
+      <x:c r="J33" s="6"/>
+      <x:c r="K33" s="6"/>
+      <x:c r="L33" s="6" t="str">
+        <x:v>Percorso relativo al modulo; collegamento da verificare nel viewer.</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34"/>
@@ -1450,6 +1349,5 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5a17a7054704108"/>
 </x:worksheet>
 </file>